--- a/product_surveys/029_earpiece_usage_feedback_form--product_surveys.xlsx
+++ b/product_surveys/029_earpiece_usage_feedback_form--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neither_satisfied_nor_dissatisfied'}</t>
+          <t>neither_satisfied_nor_dissatisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Neither Satisfied Nor Dissatisfied'}</t>
+          <t>Neither Satisfied Nor Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'battery_life_is_too_short'}</t>
+          <t>battery_life_is_too_short</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Battery Life is too short'}</t>
+          <t>Battery Life is too short</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'volume_too_soft_or_too_hard'}</t>
+          <t>volume_too_soft_or_too_hard</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Volume too soft or too hard'}</t>
+          <t>Volume too soft or too hard</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'not_loud_enough'}</t>
+          <t>not_loud_enough</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Not loud enough'}</t>
+          <t>Not loud enough</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'teams'}</t>
+          <t>teams</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Teams'}</t>
+          <t>Teams</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'retailers'}</t>
+          <t>retailers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Retailers'}</t>
+          <t>Retailers</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'device_providers'}</t>
+          <t>device_providers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Device Providers'}</t>
+          <t>Device Providers</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
